--- a/stories/arbres/ATOM-EMO.LEX.009-06.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.009-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Hippolyte est dans le salon avec maman. Coralie a le camion rouge. Les roues font un bruit doux. Hippolyte le regarde longtemps. Son ventre se serre. Ses mains restent sur ses genoux. Hippolyte dit : je suis jaloux. Maman écoute. Être jaloux n'est pas honteux. Hippolyte va près de Coralie. Il dit : je voudrais demander un tour. Coralie dit : encore un peu. Hippolyte attend la réponse. Il compte les allers du camion. Puis Coralie tend le camion. Hippolyte a son tour. Il fait rouler le camion. Maman dit : tu as nommé. Tu as demandé un tour. Tu as attendu. Plus tard, Hippolyte voit le puzzle de Coralie. Son ventre pince encore. Il se souvient. Il dit encore : je suis jaloux. Il demande un tour. Coralie dit oui. On nomme. On demande un tour. On n'attrape pas.</t>
+          <t>Hippolyte est dans le salon avec maman. Coralie a le camion rouge. Les roues font un bruit doux. Hippolyte le regarde longtemps. Son ventre se serre. Ses mains restent sur ses genoux. Je suis jaloux. Maman écoute. Être jaloux n'est pas honteux. Hippolyte va près de Coralie. Je voudrais demander un tour. Encore un peu. Hippolyte attend la réponse. Il compte les allers du camion. Puis Coralie tend le camion. Hippolyte a son tour. Il fait rouler le camion. Tu as nommé. Tu as demandé un tour. Tu as attendu. Plus tard, Hippolyte voit le puzzle de Coralie. Son ventre pince encore. Il se souvient. Il dit encore : je suis jaloux. Il demande un tour. Coralie dit oui. On nomme. On demande un tour. On n'attrape pas.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,18 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Hippolyte est dans le salon avec maman. Coralie a le camion rouge. Les roues font un bruit doux. Hippolyte le regarde longtemps. Son ventre se serre. Ses mains restent sur ses genoux.
+enfant-m|Je suis jaloux. Maman écoute. Être jaloux n'est pas honteux.
+narrateur|Hippolyte va près de Coralie.
+narrateur|Je voudrais demander un tour.
+copine|Encore un peu.
+narrateur|Hippolyte attend la réponse. Il compte les allers du camion. Puis Coralie tend le camion. Hippolyte a son tour. Il fait rouler le camion.
+maman|Tu as nommé. Tu as demandé un tour. Tu as attendu. Plus tard, Hippolyte voit le puzzle de Coralie. Son ventre pince encore.
+narrateur|Il se souvient. Il dit encore : je suis jaloux. Il demande un tour. Coralie dit oui. On nomme. On demande un tour. On n'attrape pas.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1493,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Hippolyte veut le camion. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1666,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Hippolyte a nommé : jaloux. Il a demandé un tour. Il a attendu la réponse.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1829,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Hippolyte rend le camion. Coralie reprend un tour. Maman reste près d'eux.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1996,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2036,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.009-06.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.009-06.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1317,6 +1322,7 @@
 narrateur|Il se souvient. Il dit encore : je suis jaloux. Il demande un tour. Coralie dit oui. On nomme. On demande un tour. On n'attrape pas.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1500,6 +1506,7 @@
           <t>narrateur|Hippolyte veut le camion. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1671,6 +1678,7 @@
           <t>narrateur|Hippolyte a nommé : jaloux. Il a demandé un tour. Il a attendu la réponse.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1834,6 +1842,7 @@
           <t>narrateur|Hippolyte rend le camion. Coralie reprend un tour. Maman reste près d'eux.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2001,6 +2010,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2019,7 +2029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2043,6 +2053,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2244,6 +2268,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-EMO.LEX.009-06.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.009-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hippolyte demande un tour</t>
+          <t>Le camion de Victorina</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Nino a le camion rouge. Victorina dit qu'elle est jalouse. Elle demande un tour. Elle attend. Plus tard, le puzzle. Pareil.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Hippolyte est dans le salon avec maman. Coralie a le camion rouge. Les roues font un bruit doux. Hippolyte le regarde longtemps. Son ventre se serre. Ses mains restent sur ses genoux. Je suis jaloux. Maman écoute. Être jaloux n'est pas honteux. Hippolyte va près de Coralie. Je voudrais demander un tour. Encore un peu. Hippolyte attend la réponse. Il compte les allers du camion. Puis Coralie tend le camion. Hippolyte a son tour. Il fait rouler le camion. Tu as nommé. Tu as demandé un tour. Tu as attendu. Plus tard, Hippolyte voit le puzzle de Coralie. Son ventre pince encore. Il se souvient. Il dit encore : je suis jaloux. Il demande un tour. Coralie dit oui. On nomme. On demande un tour. On n'attrape pas.</t>
+          <t>La pluie frotte la vitre du salon. Elle fait des filets, tout fins. Une lampe en papier est allumée. Elle fait un rond doux, sur le sol. Un plaid en laine attend sur le canapé. Il sent un peu le savon. Un camion rouge est sous la table. Je couds un bouton, Victorina. Nino a déjà le camion rouge. La lampe est ronde, maman. Oui. Comme une lune, sur le tapis. La pluie chante, tout bas. En ce moment, Nino fait rouler le camion. Les roues font un bruit doux. Victorina le regarde longtemps. Son ventre se serre. Ses mains restent sur ses genoux. Je suis jalouse. Je t'écoute. Être jaloux n'est pas honteux. On peut le dire. Victorina va près de Nino. Je voudrais demander un tour. Encore un peu. On attend la réponse. Victorina attend. Elle compte les allers du camion. Un. Deux. Trois. Puis Nino tend le camion. C'est ton tour. Merci, Nino. Victorina a son tour. Elle fait rouler le camion. Les roues passent dans le rond de la lampe. Tu as nommé. Tu as demandé un tour. Tu as attendu. Bravo, Victorina. Plus tard, Nino a un puzzle. Les pièces sont dans un plateau bas. Le ventre de Victorina pince encore. Je suis jalouse. Je voudrais demander un tour. Oui. Nino pousse le plateau vers elle. On nomme. On demande un tour. On attend. Les mains restent posées. J'ai demandé. J'ai attendu. Le camion reste près du pied de table. La pluie frotte encore la vitre.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1233,14 +1245,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA2" s="2" t="n">
         <v>0.96</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.12</v>
+        <v>1.28</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,14 +1324,56 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Hippolyte est dans le salon avec maman. Coralie a le camion rouge. Les roues font un bruit doux. Hippolyte le regarde longtemps. Son ventre se serre. Ses mains restent sur ses genoux.
-enfant-m|Je suis jaloux. Maman écoute. Être jaloux n'est pas honteux.
-narrateur|Hippolyte va près de Coralie.
-narrateur|Je voudrais demander un tour.
-copine|Encore un peu.
-narrateur|Hippolyte attend la réponse. Il compte les allers du camion. Puis Coralie tend le camion. Hippolyte a son tour. Il fait rouler le camion.
-maman|Tu as nommé. Tu as demandé un tour. Tu as attendu. Plus tard, Hippolyte voit le puzzle de Coralie. Son ventre pince encore.
-narrateur|Il se souvient. Il dit encore : je suis jaloux. Il demande un tour. Coralie dit oui. On nomme. On demande un tour. On n'attrape pas.</t>
+          <t>narrateur|La pluie frotte la vitre du salon.
+narrateur|Elle fait des filets, tout fins.
+narrateur|Une lampe en papier est allumée.
+narrateur|Elle fait un rond doux, sur le sol.
+narrateur|Un plaid en laine attend sur le canapé.
+narrateur|Il sent un peu le savon.
+narrateur|Un camion rouge est sous la table.
+maman|Je couds un bouton, Victorina.
+papa|Nino a déjà le camion rouge.
+enfant-f|La lampe est ronde, maman.
+maman|Oui. Comme une lune, sur le tapis.
+papa|La pluie chante, tout bas.
+narrateur|En ce moment, Nino fait rouler le camion.
+narrateur|Les roues font un bruit doux.
+narrateur|Victorina le regarde longtemps.
+narrateur|Son ventre se serre.
+narrateur|Ses mains restent sur ses genoux.
+enfant-f|Je suis jalouse.
+maman|Je t'écoute.
+papa|Être jaloux n'est pas honteux.
+maman|On peut le dire.
+narrateur|Victorina va près de Nino.
+enfant-f|Je voudrais demander un tour.
+enfant-m|Encore un peu.
+maman|On attend la réponse.
+narrateur|Victorina attend.
+narrateur|Elle compte les allers du camion.
+narrateur|Un. Deux. Trois.
+narrateur|Puis Nino tend le camion.
+enfant-m|C'est ton tour.
+enfant-f|Merci, Nino.
+narrateur|Victorina a son tour.
+narrateur|Elle fait rouler le camion.
+narrateur|Les roues passent dans le rond de la lampe.
+maman|Tu as nommé.
+maman|Tu as demandé un tour.
+papa|Tu as attendu.
+papa|Bravo, Victorina.
+narrateur|Plus tard, Nino a un puzzle.
+narrateur|Les pièces sont dans un plateau bas.
+narrateur|Le ventre de Victorina pince encore.
+enfant-f|Je suis jalouse.
+enfant-f|Je voudrais demander un tour.
+enfant-m|Oui.
+narrateur|Nino pousse le plateau vers elle.
+maman|On nomme. On demande un tour.
+papa|On attend. Les mains restent posées.
+enfant-f|J'ai demandé. J'ai attendu.
+narrateur|Le camion reste près du pied de table.
+narrateur|La pluie frotte encore la vitre.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1347,7 +1401,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Hippolyte veut le camion. Que fait-il ?</t>
+          <t>Victorina veut le camion. Que fait-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1424,14 +1478,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA3" s="2" t="n">
         <v>0.9</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1503,7 +1557,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Hippolyte veut le camion. Que fait-il ?</t>
+          <t>narrateur|Victorina veut le camion.
+narrateur|Que fait-elle ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1531,7 +1586,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Hippolyte a nommé : jaloux. Il a demandé un tour. Il a attendu la réponse.</t>
+          <t>Victorina a nommé : jalouse. Elle a demandé un tour. Elle a attendu la réponse. J'ai demandé. J'ai attendu. Oui. Le camion, puis le puzzle. Bravo. C'est du bon travail. Après, je redemande ? On demande. On attend. Les mains sur les genoux. C'est le bon geste. Le plaid en laine n'a pas bougé. Il sent encore un peu le savon. Jaloux, on le dit. Puis on demande un tour. La lampe fait toujours son rond doux.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1592,14 +1647,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA4" s="2" t="n">
         <v>0.96</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.12</v>
+        <v>1.28</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1675,7 +1730,21 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Hippolyte a nommé : jaloux. Il a demandé un tour. Il a attendu la réponse.</t>
+          <t>narrateur|Victorina a nommé : jalouse.
+narrateur|Elle a demandé un tour.
+narrateur|Elle a attendu la réponse.
+enfant-f|J'ai demandé. J'ai attendu.
+maman|Oui. Le camion, puis le puzzle.
+papa|Bravo. C'est du bon travail.
+enfant-m|Après, je redemande ?
+papa|On demande. On attend.
+enfant-f|Les mains sur les genoux.
+maman|C'est le bon geste.
+narrateur|Le plaid en laine n'a pas bougé.
+narrateur|Il sent encore un peu le savon.
+papa|Jaloux, on le dit.
+enfant-f|Puis on demande un tour.
+narrateur|La lampe fait toujours son rond doux.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1703,7 +1772,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Hippolyte rend le camion. Coralie reprend un tour. Maman reste près d'eux.</t>
+          <t>Victorina rend le camion. Nino reprend un tour. Je reste près de vous. On pose le plateau, tout doux ? Oui, papa. Merci d'avoir demandé, Victorina. Les roues font encore le bruit doux. On écoute, un peu. J'ai eu mon tour. Deux fois. Le camion, puis le puzzle. Victorina touche le plaid. La laine est un peu rêche, toute chaude. Tu as attendu Nino. Il a dit : encore un peu. La pluie ralentit sur la vitre.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1764,14 +1833,14 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA5" s="2" t="n">
         <v>0.96</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.12</v>
+        <v>1.28</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1839,7 +1908,21 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Hippolyte rend le camion. Coralie reprend un tour. Maman reste près d'eux.</t>
+          <t>narrateur|Victorina rend le camion.
+narrateur|Nino reprend un tour.
+maman|Je reste près de vous.
+papa|On pose le plateau, tout doux ?
+enfant-f|Oui, papa.
+maman|Merci d'avoir demandé, Victorina.
+enfant-m|Les roues font encore le bruit doux.
+papa|On écoute, un peu.
+enfant-f|J'ai eu mon tour.
+maman|Deux fois. Le camion, puis le puzzle.
+narrateur|Victorina touche le plaid.
+narrateur|La laine est un peu rêche, toute chaude.
+papa|Tu as attendu Nino.
+enfant-f|Il a dit : encore un peu.
+narrateur|La pluie ralentit sur la vitre.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1867,7 +1950,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'étais jalouse. J'ai demandé un tour. Tu as attendu. Bravo. Le camion rouge reste sous la table. La lampe fait encore son rond. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1928,14 +2011,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.92</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2007,7 +2090,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'étais jalouse. J'ai demandé un tour.
+maman|Tu as attendu. Bravo.
+papa|Le camion rouge reste sous la table.
+narrateur|La lampe fait encore son rond.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2029,7 +2116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2067,6 +2154,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.009-06.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.009-06.xlsx
@@ -1189,7 +1189,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Hippolyte est dans le salon avec maman. Coralie a le camion rouge. Les roues font un bruit doux. Hippolyte le regarde longtemps. Son ventre se serre. Ses mains restent sur ses genoux. Hippolyte dit : je suis &lt;emphasis level="moderate"&gt;jaloux&lt;/emphasis&gt;. Maman écoute. Être jaloux n'est pas honteux. Hippolyte va près de Coralie. Il dit : je voudrais demander un tour. Coralie dit : encore un peu. Hippolyte attend la réponse. Il compte les allers du camion. Puis Coralie tend le camion. Hippolyte a son tour. Il fait rouler le camion. Maman dit : tu as nommé. Tu as demandé un tour. Tu as attendu. Plus tard, Hippolyte voit le puzzle de Coralie. Son ventre pince encore. Il se souvient. Il dit encore : je suis jaloux. Il demande un tour. Coralie dit oui. On nomme. On demande un tour. On n'attrape pas.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La pluie frotte la vitre du salon. Elle fait des filets, tout fins. Une lampe en papier est allumée. Elle fait un rond doux, sur le sol. Un plaid en laine attend sur le canapé. Il sent un peu le savon. Un camion rouge est sous la table. Je couds un bouton, Victorina. Nino a déjà le camion rouge. La lampe est ronde, maman. Oui. Comme une lune, sur le tapis. La pluie chante, tout bas. En ce moment, Nino fait rouler le camion. Les roues font un bruit doux. Victorina le regarde longtemps. Son ventre se serre. Ses mains restent sur ses genoux. Je suis jalouse. Je t'écoute. Être jaloux n'est pas honteux. On peut le dire. Victorina va près de Nino. Je voudrais demander un tour. Encore un peu. On attend la réponse. Victorina attend. Elle compte les allers du camion. Un. Deux. Trois. Puis Nino tend le camion. C'est ton tour. Merci, Nino. Victorina a son tour. Elle fait rouler le camion. Les roues passent dans le rond de la lampe. Tu as nommé. Tu as demandé un tour. Tu as attendu. Bravo, Victorina. Plus tard, Nino a un puzzle. Les pièces sont dans un plateau bas. Le ventre de Victorina pince encore. Je suis jalouse. Je voudrais demander un tour. Oui. Nino pousse le plateau vers elle. On nomme. On demande un tour. On attend. Les mains restent posées. J'ai demandé. J'ai attendu. Le camion reste près du pied de table. La pluie frotte encore la vitre.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1376,7 +1376,6 @@
 narrateur|La pluie frotte encore la vitre.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1406,7 +1405,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Hippolyte veut le camion. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorina veut le camion. Que fait-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1561,7 +1560,6 @@
 narrateur|Que fait-elle ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1586,12 +1584,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Victorina a nommé : jalouse. Elle a demandé un tour. Elle a attendu la réponse. J'ai demandé. J'ai attendu. Oui. Le camion, puis le puzzle. Bravo. C'est du bon travail. Après, je redemande ? On demande. On attend. Les mains sur les genoux. C'est le bon geste. Le plaid en laine n'a pas bougé. Il sent encore un peu le savon. Jaloux, on le dit. Puis on demande un tour. La lampe fait toujours son rond doux.</t>
+          <t>Victorina a nommé : jalouse. Elle a demandé un tour. Elle a attendu la réponse. J'ai demandé. J'ai attendu. Oui. Le camion, puis le puzzle. Après, je redemande ? On demande. On attend. Les mains sur les genoux. C'est le bon geste. Le plaid en laine n'a pas bougé. Il sent encore un peu le savon. Jaloux, on le dit. Puis on demande un tour. La lampe fait toujours son rond doux.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Hippolyte a nommé : &lt;emphasis level="moderate"&gt;jaloux&lt;/emphasis&gt;. Il a demandé un tour. Il a attendu la réponse.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorina a nommé : jalouse. Elle a demandé un tour. Elle a attendu la réponse. J'ai demandé. J'ai attendu. Oui. Le camion, puis le puzzle. Après, je redemande ? On demande. On attend. Les mains sur les genoux. C'est le bon geste. Le plaid en laine n'a pas bougé. Il sent encore un peu le savon. Jaloux, on le dit. Puis on demande un tour. La lampe fait toujours son rond doux.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1735,7 +1733,6 @@
 narrateur|Elle a attendu la réponse.
 enfant-f|J'ai demandé. J'ai attendu.
 maman|Oui. Le camion, puis le puzzle.
-papa|Bravo. C'est du bon travail.
 enfant-m|Après, je redemande ?
 papa|On demande. On attend.
 enfant-f|Les mains sur les genoux.
@@ -1747,7 +1744,6 @@
 narrateur|La lampe fait toujours son rond doux.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1777,7 +1773,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Hippolyte rend le camion. Coralie reprend un tour. Maman reste près d'eux.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorina rend le camion. Nino reprend un tour. Je reste près de vous. On pose le plateau, tout doux ? Oui, papa. Merci d'avoir demandé, Victorina. Les roues font encore le bruit doux. On écoute, un peu. J'ai eu mon tour. Deux fois. Le camion, puis le puzzle. Victorina touche le plaid. La laine est un peu rêche, toute chaude. Tu as attendu Nino. Il a dit : encore un peu. La pluie ralentit sur la vitre.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1925,7 +1921,6 @@
 narrateur|La pluie ralentit sur la vitre.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1950,12 +1945,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'étais jalouse. J'ai demandé un tour. Tu as attendu. Bravo. Le camion rouge reste sous la table. La lampe fait encore son rond. L'histoire est finie.</t>
+          <t>J'étais jalouse. J'ai demandé un tour. Tu as attendu. Bravo. Le camion rouge reste sous la table. La lampe fait encore son rond.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'étais jalouse. J'ai demandé un tour. Tu as attendu. Bravo. Le camion rouge reste sous la table. La lampe fait encore son rond.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2093,11 +2088,9 @@
           <t>enfant-f|J'étais jalouse. J'ai demandé un tour.
 maman|Tu as attendu. Bravo.
 papa|Le camion rouge reste sous la table.
-narrateur|La lampe fait encore son rond.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|La lampe fait encore son rond.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2116,7 +2109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2161,6 +2154,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.009-06.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.009-06.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hippolyte, Coralie, maman</t>
+          <t>Victorina, Nino, papa, maman</t>
         </is>
       </c>
     </row>
